--- a/02.舞台美術/切り出し寸法.xlsx
+++ b/02.舞台美術/切り出し寸法.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01.ドキュメント\01.劇団抜きにくい釘\07.個人\蒼樹とも\01.参加公演\WAN-WAN-BOTAN-2026\02.舞台美術\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\青木智之\Desktop\aoki\files\2026.03 WAN-WAN BOTAN\02.舞台美術\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F7E024-9DEE-441C-AA26-268DAE5508B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BD5D08-B377-4866-9EDF-446B1532A895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="60">
   <si>
     <t>ドア上部（パネル）</t>
     <rPh sb="2" eb="4">
@@ -262,6 +273,172 @@
     <t>窓</t>
     <rPh sb="0" eb="1">
       <t>マド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製作方法不明</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>フメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル①（本体）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>225 * 1800</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3本</t>
+    <rPh sb="1" eb="2">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル①（上部）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>225 * 600</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>648 * 1800</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>648 * 600</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル②（本体）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル②（上部）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル③（本体）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>135 * 600</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整パネル③（上部）</t>
+    <rPh sb="0" eb="3">
+      <t>ビチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>135 * 1800</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スロープ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1000 * 900</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1000 * 900（102 - 0）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 * 4材</t>
+    <rPh sb="5" eb="6">
+      <t>ザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微調整平台</t>
+    <rPh sb="0" eb="1">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒラダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>900 * 1800 * 115</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>900 * 1800</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寸角</t>
+    <rPh sb="0" eb="1">
+      <t>スン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -271,7 +448,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0&quot;mm&quot;"/>
+    <numFmt numFmtId="176" formatCode="0&quot;mm&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -353,10 +530,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -642,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E54"/>
+  <dimension ref="B2:E104"/>
   <sheetFormatPr defaultColWidth="3.69921875" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.69921875" style="1"/>
@@ -1140,41 +1317,537 @@
       <c r="E51" s="3"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <f>225-32</f>
+        <v>193</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="5">
+        <v>600</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="B66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="5">
+        <f>225-32</f>
+        <v>193</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70" spans="2:5">
+      <c r="B70" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="5">
+        <f>648-32</f>
+        <v>616</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="B73" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="B75" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="B76" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="5">
+        <v>600</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="B78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="5">
+        <f>648-32</f>
+        <v>616</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="2:5">
+      <c r="B79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="81" spans="2:5">
+      <c r="B81" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="B82" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E82" s="7"/>
+    </row>
+    <row r="83" spans="2:5">
+      <c r="B83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="5">
+        <f>135-32</f>
+        <v>103</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E88" s="7"/>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="5">
+        <v>600</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="5">
+        <f>135-32</f>
+        <v>103</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="B93" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+    </row>
+    <row r="94" spans="2:5">
+      <c r="B94" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="7"/>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="B95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C95" s="5">
+        <f>900-38</f>
+        <v>862</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="2:5">
+      <c r="B96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C96" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="B99" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="B100" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="7"/>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C102" s="5">
+        <f>900-76</f>
+        <v>824</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="2:5">
+      <c r="B103" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C103" s="5">
+        <f>900-76</f>
+        <v>824</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="B104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E104" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="51">
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:E8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/02.舞台美術/切り出し寸法.xlsx
+++ b/02.舞台美術/切り出し寸法.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\青木智之\Desktop\aoki\files\2026.03 WAN-WAN BOTAN\02.舞台美術\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BD5D08-B377-4866-9EDF-446B1532A895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF559912-AA71-4582-A077-DC6AC36D4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1797,6 +1797,48 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:E82"/>
     <mergeCell ref="D100:E100"/>
     <mergeCell ref="B100:C100"/>
     <mergeCell ref="B99:E99"/>
@@ -1806,50 +1848,9 @@
     <mergeCell ref="D94:E94"/>
     <mergeCell ref="B94:C94"/>
     <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="75" fitToWidth="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>